--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.4556487102501</v>
+        <v>5.274042915415642</v>
       </c>
       <c r="D2" t="n">
-        <v>34.19180963822451</v>
+        <v>5.556169066211483</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38071498810579</v>
+        <v>2.174366185567191</v>
       </c>
       <c r="F2" t="n">
-        <v>17.19965235777863</v>
+        <v>2.794943508139027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.09115483647451</v>
+        <v>3.914812660927107</v>
       </c>
       <c r="D3" t="n">
-        <v>23.96794214320139</v>
+        <v>3.894790598270226</v>
       </c>
       <c r="E3" t="n">
-        <v>13.38071498810579</v>
+        <v>2.174366185567191</v>
       </c>
       <c r="F3" t="n">
-        <v>17.19965235777863</v>
+        <v>2.794943508139027</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.42912314176901</v>
+        <v>4.944732510537464</v>
       </c>
       <c r="D4" t="n">
-        <v>59.17668007750364</v>
+        <v>9.616210512594343</v>
       </c>
       <c r="E4" t="n">
-        <v>13.38071498810579</v>
+        <v>2.174366185567191</v>
       </c>
       <c r="F4" t="n">
-        <v>17.19965235777863</v>
+        <v>2.794943508139027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.61389218954498</v>
+        <v>9.84975748080106</v>
       </c>
       <c r="D5" t="n">
-        <v>59.94973201826389</v>
+        <v>9.741831452967883</v>
       </c>
       <c r="E5" t="n">
-        <v>13.38071498810579</v>
+        <v>2.174366185567191</v>
       </c>
       <c r="F5" t="n">
-        <v>17.19965235777863</v>
+        <v>2.794943508139027</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.32280618398265</v>
+        <v>4.114956004897182</v>
       </c>
       <c r="D6" t="n">
-        <v>19.38802309822599</v>
+        <v>3.150553753461724</v>
       </c>
       <c r="E6" t="n">
-        <v>13.38071498810579</v>
+        <v>2.174366185567191</v>
       </c>
       <c r="F6" t="n">
-        <v>17.19965235777863</v>
+        <v>2.794943508139027</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
